--- a/KatalonData/IWPTestData/EmulatorData.xlsx
+++ b/KatalonData/IWPTestData/EmulatorData.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\katalon\VPS-Katalon\KatalonData\IWPTestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D41F04-0492-4236-B243-4E5BC4C955E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D07370D1-A196-4CA7-951F-BB13CF072275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B75285DF-1640-4994-93D2-6C318038763B}"/>
+    <workbookView xWindow="2652" yWindow="2100" windowWidth="17280" windowHeight="9972" xr2:uid="{B75285DF-1640-4994-93D2-6C318038763B}"/>
   </bookViews>
   <sheets>
     <sheet name="EmulatorData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="142">
   <si>
     <t>Notes</t>
   </si>
@@ -443,6 +442,15 @@
   </si>
   <si>
     <t>|Yoghurt~Organic~$45~125cal~Sep3rd~AI~RiteAid|</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>36</t>
   </si>
 </sst>
 </file>
@@ -816,40 +824,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D3E213-FD08-482B-9ECE-5B5E0D45C129}">
-  <dimension ref="A1:AF34"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AF37"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="4" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.7109375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.6640625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="25" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="16.42578125" style="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.28515625" style="1"/>
+    <col min="31" max="31" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16.44140625" style="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -947,7 +955,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
@@ -1027,7 +1035,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>52</v>
       </c>
@@ -1051,7 +1059,7 @@
       </c>
       <c r="S3" s="2"/>
     </row>
-    <row r="4" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>56</v>
       </c>
@@ -1128,7 +1136,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>59</v>
       </c>
@@ -1148,7 +1156,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>71</v>
       </c>
@@ -1228,7 +1236,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="s">
         <v>73</v>
       </c>
@@ -1290,7 +1298,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>51</v>
       </c>
@@ -1355,7 +1363,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>51</v>
       </c>
@@ -1438,7 +1446,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>51</v>
       </c>
@@ -1521,7 +1529,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>94</v>
       </c>
@@ -1557,7 +1565,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>99</v>
       </c>
@@ -1611,7 +1619,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>94</v>
       </c>
@@ -1644,7 +1652,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>94</v>
       </c>
@@ -1679,7 +1687,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>94</v>
       </c>
@@ -1715,7 +1723,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>51</v>
       </c>
@@ -1798,7 +1806,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>99</v>
       </c>
@@ -1852,7 +1860,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>94</v>
       </c>
@@ -1884,7 +1892,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>94</v>
       </c>
@@ -1916,7 +1924,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>56</v>
       </c>
@@ -1996,7 +2004,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>110</v>
       </c>
@@ -2073,7 +2081,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>110</v>
       </c>
@@ -2150,7 +2158,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>110</v>
       </c>
@@ -2227,7 +2235,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>110</v>
       </c>
@@ -2304,7 +2312,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:32" ht="60" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>110</v>
       </c>
@@ -2384,7 +2392,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="26" spans="1:32" ht="60" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>110</v>
       </c>
@@ -2464,7 +2472,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>110</v>
       </c>
@@ -2541,7 +2549,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>110</v>
       </c>
@@ -2618,7 +2626,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>110</v>
       </c>
@@ -2695,7 +2703,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>110</v>
       </c>
@@ -2772,7 +2780,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:32" ht="60" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>110</v>
       </c>
@@ -2852,7 +2860,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>110</v>
       </c>
@@ -2929,7 +2937,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>110</v>
       </c>
@@ -3006,7 +3014,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>110</v>
       </c>
@@ -3080,6 +3088,101 @@
         <v>49</v>
       </c>
       <c r="AC34" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S35" s="2"/>
+      <c r="W35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S36" s="2"/>
+      <c r="W36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC37" s="1" t="s">
         <v>50</v>
       </c>
     </row>
